--- a/flow/20231226_zachala_month/month_readings.xlsx
+++ b/flow/20231226_zachala_month/month_readings.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\GitHub\prayer-service-scripts\flow\20231226_zachala_month\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CAC67D-324A-4975-92D2-41489B3D55EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B368526-BB71-4545-9BCA-7DD1422C4314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10710" yWindow="1005" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2325" yWindow="1920" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2024-5-u" sheetId="1" r:id="rId1"/>
-    <sheet name="2024-05-g" sheetId="2" r:id="rId2"/>
+    <sheet name="2024-06-u" sheetId="5" r:id="rId1"/>
+    <sheet name="2024-06-g" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_2024_5_g" localSheetId="1">'2024-05-g'!$A$1:$K$31</definedName>
-    <definedName name="_2024_5_u" localSheetId="0">'2024-5-u'!$A$1:$Q$31</definedName>
+    <definedName name="_2024_5_g" localSheetId="1">'2024-06-g'!$A$1:$K$30</definedName>
+    <definedName name="_2024_5_u" localSheetId="0">'2024-06-u'!$A$1:$K$30</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -26,8 +26,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="2024-5-g" type="6" refreshedVersion="7" background="1" saveData="1">
-    <textPr codePage="65001" sourceFile="C:\Work\GitHub\prayer-service-scripts\flow\20231226_zachala_month\2024-5-g.csv" decimal="," thousands=" " tab="0" comma="1">
+  <connection id="1" xr16:uid="{BABDD354-1F14-4F5A-94B1-A4274724EE60}" name="2024-5-g1" type="6" refreshedVersion="7" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="C:\Work\GitHub\prayer-service-scripts\flow\20231226_zachala_month\2024-6-g.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="11">
         <textField type="text"/>
         <textField type="text"/>
@@ -43,8 +43,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="2024-5-u" type="6" refreshedVersion="7" background="1" saveData="1">
-    <textPr codePage="65001" sourceFile="C:\Work\GitHub\prayer-service-scripts\flow\20231226_zachala_month\2024-5-u.csv" decimal="," thousands=" " tab="0" comma="1">
+  <connection id="2" xr16:uid="{F76BDC15-4647-4717-BD11-E05FC3397B5F}" name="2024-5-u1" type="6" refreshedVersion="7" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="C:\Work\GitHub\prayer-service-scripts\flow\20231226_zachala_month\2024-6-u.csv" decimal="," thousands=" " tab="0" comma="1">
       <textFields count="17">
         <textField type="text"/>
         <textField type="text"/>
@@ -70,13 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="241">
-  <si>
-    <t>Травень</t>
-  </si>
-  <si>
-    <t>01.05</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="230">
   <si>
     <t>3</t>
   </si>
@@ -84,564 +78,135 @@
     <t>ср</t>
   </si>
   <si>
-    <t>Велика середа. Св. прор. Єремії Блаж. сщмч. Климентія Шептицького, архим. Унівського</t>
-  </si>
-  <si>
-    <t>02.05</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
     <t>чт</t>
   </si>
   <si>
-    <t>Великий четвер. 🕃 Св. отця Атанасія Великого, аєп. Олександрійського</t>
-  </si>
-  <si>
-    <t>03.05</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
     <t>пт</t>
   </si>
   <si>
-    <t>Велика п’ятниця.&lt;/em&gt; 🕂 Переставл. прп. Теодосія, ігум. монастиря Печерського, спільного життя засновника Свв. мчч. Тимотея й Маври</t>
-  </si>
-  <si>
-    <t>04.05</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
     <t>сб</t>
   </si>
   <si>
-    <t>Велика субота. Св. мц. Пелагії</t>
-  </si>
-  <si>
-    <t>05.05</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
     <t>нд</t>
   </si>
   <si>
-    <t>🕀 Неділя Пасхи. Воскресення Христове. Великдень. Св. і славн. мц. Ірини Прп. Никифора, ігум. монастиря Мидікійського</t>
-  </si>
-  <si>
-    <t>#iv001</t>
-  </si>
-  <si>
-    <t>06.05</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
     <t>пн</t>
   </si>
   <si>
-    <t>Світлий понеділок. Тиждень загальниці. Св., і прав., і багатостражд. Йова</t>
-  </si>
-  <si>
-    <t>#ap002</t>
-  </si>
-  <si>
-    <t>#iv002</t>
-  </si>
-  <si>
-    <t>07.05</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>вв</t>
   </si>
   <si>
-    <t>Світлий вівторок. 🕃 Спогад про явління на небі знамення чесного Хреста у св. місті Єрусалимі Св. мч. Акакія</t>
-  </si>
-  <si>
-    <t>#ap004</t>
-  </si>
-  <si>
-    <t>#lk113</t>
-  </si>
-  <si>
-    <t>08.05</t>
-  </si>
-  <si>
-    <t>Світла середа. 🕁 Св. ап. і єв. Івана Богослова Прп. Арсенія Великого</t>
-  </si>
-  <si>
     <t>Ряд.:</t>
   </si>
   <si>
     <t>Ап.:</t>
   </si>
   <si>
-    <t>#ap005</t>
-  </si>
-  <si>
-    <t>#ap068b</t>
-  </si>
-  <si>
-    <t>#iv004</t>
-  </si>
-  <si>
-    <t>#iv061b</t>
-  </si>
-  <si>
-    <t>09.05</t>
-  </si>
-  <si>
-    <t>Світлий четвер. 🕂 Перенесення чесних мощів св. Миколая Чудотворця з Мир до міста Барі Св. прор. Ісаї Св. мч. Христофора</t>
-  </si>
-  <si>
-    <t>Св. Миколая:</t>
-  </si>
-  <si>
-    <t>#ap006</t>
-  </si>
-  <si>
-    <t>#ap335</t>
-  </si>
-  <si>
-    <t>#iv008</t>
-  </si>
-  <si>
-    <t>#lk024</t>
-  </si>
-  <si>
-    <t>10.05</t>
-  </si>
-  <si>
-    <t>Світла п’ятниця. 🕂 Св. ап. Симона Зилота</t>
-  </si>
-  <si>
-    <t>#ap007</t>
-  </si>
-  <si>
     <t>#ap131</t>
   </si>
   <si>
-    <t>#iv007</t>
-  </si>
-  <si>
-    <t>#mt056</t>
-  </si>
-  <si>
-    <t>11.05</t>
-  </si>
-  <si>
-    <t>Світла субота. 🕂 Свв. рівноапп. Кирила й Методія, учителів слов’янських Св. сщмч. Мокія</t>
-  </si>
-  <si>
-    <t>Рівноап.:</t>
-  </si>
-  <si>
-    <t>#ap008</t>
-  </si>
-  <si>
-    <t>#ap318a</t>
-  </si>
-  <si>
-    <t>#iv011</t>
-  </si>
-  <si>
-    <t>#iv036</t>
-  </si>
-  <si>
-    <t>12.05</t>
-  </si>
-  <si>
-    <t>Неділя 2-га після Пасхи. Томина. Антипасха. Свв. Епіфанія, єп. Кипрського, і Германа, патр. Царгородського</t>
-  </si>
-  <si>
-    <t>#ap014</t>
-  </si>
-  <si>
-    <t>#iv065a</t>
-  </si>
-  <si>
-    <t>13.05</t>
-  </si>
-  <si>
-    <t>Тиждень 2-ий після Пасхи. Св. мц. Гликерії</t>
-  </si>
-  <si>
-    <t>#ap009</t>
-  </si>
-  <si>
-    <t>#iv006</t>
-  </si>
-  <si>
-    <t>14.05</t>
-  </si>
-  <si>
-    <t>Св. мч. Ісидора</t>
-  </si>
-  <si>
-    <t>#ap010</t>
-  </si>
-  <si>
-    <t>#iv010</t>
-  </si>
-  <si>
-    <t>15.05</t>
-  </si>
-  <si>
-    <t>🕃 Прп. Пахомія Великого</t>
-  </si>
-  <si>
-    <t>#ap011</t>
-  </si>
-  <si>
-    <t>#iv015</t>
-  </si>
-  <si>
-    <t>16.05</t>
-  </si>
-  <si>
-    <t>Прп. Теодора Освященного, учня св. Пахомія Блаж. сщмчч. Северіана Бараника, Якима Сенківського, Віталія Байрака</t>
-  </si>
-  <si>
-    <t>#ap012</t>
-  </si>
-  <si>
     <t>#iv016</t>
   </si>
   <si>
-    <t>17.05</t>
-  </si>
-  <si>
-    <t>Св. ап. Андроніка і тих, що з ним Блаж. сщмч. Івана Зятика</t>
-  </si>
-  <si>
-    <t>#ap013</t>
-  </si>
-  <si>
-    <t>#iv017</t>
-  </si>
-  <si>
-    <t>18.05</t>
-  </si>
-  <si>
-    <t>Св. мч. Теодота (Богдана), що в Анкирі Свв. мчч. Петра, Діонісія і тих, що з ними Свв. сімох дів</t>
-  </si>
-  <si>
-    <t>#ap015</t>
-  </si>
-  <si>
-    <t>#iv019</t>
-  </si>
-  <si>
-    <t>19.05</t>
-  </si>
-  <si>
-    <t>Неділя 3-я після Пасхи. Мироносиць. Св. сщмч. Патрикія, єп. Пруського, і тих, що з ним</t>
-  </si>
-  <si>
-    <t>#ap016</t>
-  </si>
-  <si>
-    <t>#mr069a</t>
-  </si>
-  <si>
-    <t>20.05</t>
-  </si>
-  <si>
-    <t>Тиждень 3-ій після Пасхи. Св. мч. Талалея</t>
-  </si>
-  <si>
-    <t>#ap017</t>
-  </si>
-  <si>
-    <t>#iv013</t>
-  </si>
-  <si>
-    <t>21.05</t>
-  </si>
-  <si>
-    <t>🕂 Свв. великих царів і рівноапп. Константина й Олени</t>
-  </si>
-  <si>
-    <t>#ap018</t>
-  </si>
-  <si>
-    <t>#iv020</t>
-  </si>
-  <si>
-    <t>#iv035b</t>
-  </si>
-  <si>
-    <t>22.05</t>
-  </si>
-  <si>
-    <t>Св. мч. Василіска</t>
-  </si>
-  <si>
-    <t>#ap019</t>
-  </si>
-  <si>
-    <t>#iv021</t>
-  </si>
-  <si>
-    <t>23.05</t>
-  </si>
-  <si>
-    <t>Прп. Євфросинії Полоцької, ігум. монастиря Св. Спаса Прп. й ісп. Михаїла, єп. Синадського</t>
-  </si>
-  <si>
-    <t>#ap020</t>
-  </si>
-  <si>
-    <t>#iv022</t>
-  </si>
-  <si>
-    <t>24.05</t>
-  </si>
-  <si>
-    <t>🕃 Прп. Микити, стовпника, переяславського чудотв. 🕃 Прп. Симеона, що на Дивній горі</t>
-  </si>
-  <si>
-    <t>#ap021a</t>
-  </si>
-  <si>
-    <t>#iv023</t>
-  </si>
-  <si>
-    <t>25.05</t>
-  </si>
-  <si>
-    <t>🕂 Третє віднайдення чесної голови св. і славн. прор., предтечі і хрестителя Господнього Івана Блаж. сщмч. Миколи Цегельського, пресвіт.</t>
-  </si>
-  <si>
     <t>Предтечі:</t>
   </si>
   <si>
-    <t>#ap022</t>
-  </si>
-  <si>
-    <t>#ap176</t>
-  </si>
-  <si>
-    <t>#iv052</t>
-  </si>
-  <si>
     <t>#mt040</t>
   </si>
   <si>
-    <t>26.05</t>
-  </si>
-  <si>
-    <t>Неділя 4-та після Пасхи, розслабленого. Св. ап. Карпа, одного із сімдесятьох</t>
-  </si>
-  <si>
-    <t>#ap023</t>
-  </si>
-  <si>
-    <t>#iv014a</t>
-  </si>
-  <si>
-    <t>27.05</t>
-  </si>
-  <si>
-    <t>Тиждень 4-ий після Пасхи. Св. сщмч. Терапонта</t>
-  </si>
-  <si>
-    <t>#ap024</t>
-  </si>
-  <si>
-    <t>#iv024</t>
-  </si>
-  <si>
-    <t>28.05</t>
-  </si>
-  <si>
-    <t>Прп. Микити, єп. Халкедонського</t>
-  </si>
-  <si>
-    <t>#ap025</t>
-  </si>
-  <si>
-    <t>#iv025</t>
-  </si>
-  <si>
-    <t>29.05</t>
-  </si>
-  <si>
-    <t>Переполовення П’ятдесятниці. Св. прпмц. Теодосії, діви</t>
-  </si>
-  <si>
-    <t>#ap034</t>
-  </si>
-  <si>
-    <t>#iv026</t>
-  </si>
-  <si>
-    <t>30.05</t>
-  </si>
-  <si>
-    <t>Прп. Ісаакія, ігум. обителі Далматської</t>
-  </si>
-  <si>
-    <t>#ap026</t>
-  </si>
-  <si>
-    <t>#iv029</t>
-  </si>
-  <si>
-    <t>31.05</t>
-  </si>
-  <si>
-    <t>Св. ап. Єрмія Св. мч. Єрмея</t>
-  </si>
-  <si>
-    <t>#ap027</t>
-  </si>
-  <si>
-    <t>#iv030</t>
-  </si>
-  <si>
-    <t>Віддання свята Переполовення. Св. прор. Єремії Блаж. сщмч. Климентія Шептицького, архим. Унівського</t>
-  </si>
-  <si>
     <t>#ap032</t>
   </si>
   <si>
     <t>#iv018</t>
   </si>
   <si>
-    <t>🕃 Св. отця Атанасія Великого, аєп. Олександрійського</t>
-  </si>
-  <si>
     <t>#ap035</t>
   </si>
   <si>
     <t>#iv035a</t>
   </si>
   <si>
-    <t>🕂 Переставл. прп. Теодосія, ігум. монастиря Печерського, спільного життя засновника Свв. мчч. Тимотея й Маври</t>
-  </si>
-  <si>
-    <t>Прп.:</t>
-  </si>
-  <si>
     <t>#ap036</t>
   </si>
   <si>
-    <t>#ap334</t>
-  </si>
-  <si>
     <t>#iv037a</t>
   </si>
   <si>
     <t>#mt043</t>
   </si>
   <si>
-    <t>Св. мц. Пелагії</t>
-  </si>
-  <si>
     <t>#ap037</t>
   </si>
   <si>
     <t>#iv038</t>
   </si>
   <si>
-    <t>Неділя 6-та після Пасхи, сліпородженого. Св. і славн. мц. Ірини Прп. Никифора, ігум. монастиря Мидікійського</t>
-  </si>
-  <si>
     <t>#ap038</t>
   </si>
   <si>
     <t>#iv034</t>
   </si>
   <si>
-    <t>Тиждень 6-ий після Пасхи. Св., і прав., і багатостражд. Йова</t>
-  </si>
-  <si>
     <t>#ap039</t>
   </si>
   <si>
     <t>#iv040</t>
   </si>
   <si>
-    <t>🕃 Спогад про явління на небі знамення чесного Хреста у св. місті Єрусалимі Св. мч. Акакія</t>
-  </si>
-  <si>
-    <t>Хреста:</t>
-  </si>
-  <si>
     <t>#ap040a</t>
   </si>
   <si>
-    <t>#ap125a</t>
-  </si>
-  <si>
     <t>#iv042a</t>
   </si>
   <si>
-    <t>#iv060</t>
-  </si>
-  <si>
-    <t>Віддання Пасхи. 🕁 Св. ап. і єв. Івана Богослова Прп. Арсенія Великого</t>
-  </si>
-  <si>
     <t>#ap041</t>
   </si>
   <si>
     <t>#iv043</t>
   </si>
   <si>
-    <t>🕀 Вознесіння Господнє. 🕂 Перенесення чесних мощів св. Миколая Чудотворця з Мир до міста Барі Св. прор. Ісаї Св. мч. Христофора</t>
-  </si>
-  <si>
-    <t>Свята.:</t>
-  </si>
-  <si>
     <t>#ap001b</t>
   </si>
   <si>
     <t>#lk114</t>
   </si>
   <si>
-    <t>🕂 Св. ап. Симона Зилота</t>
-  </si>
-  <si>
     <t>#ap042</t>
   </si>
   <si>
     <t>#iv047</t>
   </si>
   <si>
-    <t>🕂 Свв. рівноапп. Кирила й Методія, учителів слов’янських Св. сщмч. Мокія</t>
-  </si>
-  <si>
     <t>#ap043</t>
   </si>
   <si>
     <t>#iv048a</t>
   </si>
   <si>
-    <t>Неділя 7-ма після Пасхи, свв. отців I-го Вселенського Собору. Свв. Епіфанія, єп. Кипрського, і Германа, патр. Царгородського</t>
-  </si>
-  <si>
     <t>#ap044</t>
   </si>
   <si>
     <t>#iv056</t>
   </si>
   <si>
-    <t>Тиждень 7-ий після Пасхи. Св. мц. Гликерії</t>
-  </si>
-  <si>
     <t>#ap045</t>
   </si>
   <si>
@@ -666,18 +231,12 @@
     <t>#iv055</t>
   </si>
   <si>
-    <t>Віддання Вознесіння. Св. ап. Андроніка і тих, що з ним Блаж. сщмч. Івана Зятика</t>
-  </si>
-  <si>
     <t>#ap050a</t>
   </si>
   <si>
     <t>#iv057</t>
   </si>
   <si>
-    <t>Субота заупокійна. Св. мч. Теодота (Богдана), що в Анкирі Свв. мчч. Петра, Діонісія і тих, що з ними Свв. сімох дів</t>
-  </si>
-  <si>
     <t>За упокій:</t>
   </si>
   <si>
@@ -690,18 +249,12 @@
     <t>#iv067</t>
   </si>
   <si>
-    <t>🕀 Зіслання Святого Духа. П’ятдесятниця. Св. сщмч. Патрикія, єп. Пруського, і тих, що з ним</t>
-  </si>
-  <si>
     <t>#ap003</t>
   </si>
   <si>
     <t>#iv027</t>
   </si>
   <si>
-    <t>Понеділок Святого Духа.  Тиждень 1-ий по Зісланні Святого Духа. Тиждень загальниці. Св. мч. Талалея</t>
-  </si>
-  <si>
     <t>#ap229</t>
   </si>
   <si>
@@ -711,9 +264,6 @@
     <t>#ap079a</t>
   </si>
   <si>
-    <t>#ap049</t>
-  </si>
-  <si>
     <t>#mt010a</t>
   </si>
   <si>
@@ -723,76 +273,493 @@
     <t>#mt012</t>
   </si>
   <si>
-    <t>#ap081a</t>
-  </si>
-  <si>
-    <t>#mt013</t>
-  </si>
-  <si>
     <t>#ap082</t>
   </si>
   <si>
     <t>#mt014</t>
   </si>
   <si>
-    <t>Віддання П’ятдесятниці.🕂 Третє віднайдення чесної голови св. і славн. прор., предтечі і хрестителя Господнього Івана Блаж. сщмч. Миколи Цегельського, пресвіт.</t>
-  </si>
-  <si>
     <t>#ap079b</t>
   </si>
   <si>
     <t>#mt015</t>
   </si>
   <si>
-    <t>Неділя 1-ша по Зісланні Святого Духа. Всіх святих. Св. ап. Карпа, одного із сімдесятьох</t>
-  </si>
-  <si>
     <t>#ap330</t>
   </si>
   <si>
     <t>#mt038a</t>
   </si>
   <si>
-    <t>Тиждень 2-ий по Зісланні Святого Духа. Початок Петрового посту. Св. сщмч. Терапонта</t>
-  </si>
-  <si>
-    <t>#ap083</t>
-  </si>
-  <si>
-    <t>#mt019</t>
-  </si>
-  <si>
-    <t>#ap086</t>
-  </si>
-  <si>
-    <t>#mt022</t>
-  </si>
-  <si>
-    <t>Св. прпмц. Теодосії, діви</t>
-  </si>
-  <si>
-    <t>#ap087</t>
-  </si>
-  <si>
-    <t>#mt023</t>
-  </si>
-  <si>
-    <t>🕀 Торжественне поклоніння пречистим Тайнам Тіла і Крови Господа нашого Ісуса Христа. Прп. Ісаакія, ігум. обителі Далматської</t>
-  </si>
-  <si>
     <t>Свята:</t>
   </si>
   <si>
-    <t>#ap149</t>
-  </si>
-  <si>
-    <t>#ap090</t>
-  </si>
-  <si>
-    <t>#mt031</t>
-  </si>
-  <si>
-    <t>#ap001a</t>
+    <t>Червень</t>
+  </si>
+  <si>
+    <t>01.06</t>
+  </si>
+  <si>
+    <t>Св. мч. Юстина, філософа, і тих, що з ним</t>
+  </si>
+  <si>
+    <t>#ap029</t>
+  </si>
+  <si>
+    <t>#iv031</t>
+  </si>
+  <si>
+    <t>02.06</t>
+  </si>
+  <si>
+    <t>Неділя 5-та після Пасхи, самарянки. Св. Никифора, ісп.</t>
+  </si>
+  <si>
+    <t>#ap028</t>
+  </si>
+  <si>
+    <t>#iv012</t>
+  </si>
+  <si>
+    <t>03.06</t>
+  </si>
+  <si>
+    <t>Тиждень 5-ий після Пасхи. Св. мч. Лукиліяна і тих, що з ним</t>
+  </si>
+  <si>
+    <t>#ap030</t>
+  </si>
+  <si>
+    <t>#iv032</t>
+  </si>
+  <si>
+    <t>04.06</t>
+  </si>
+  <si>
+    <t>Св. Митрофана, патр. Царгородського</t>
+  </si>
+  <si>
+    <t>#ap031</t>
+  </si>
+  <si>
+    <t>#iv033</t>
+  </si>
+  <si>
+    <t>05.06</t>
+  </si>
+  <si>
+    <t>Віддання свята Преполовення. Св. сщмч. Доротея, єп. Тирського Св. мч. Косми, пресвіт. вірменського</t>
+  </si>
+  <si>
+    <t>06.06</t>
+  </si>
+  <si>
+    <t>Прп. Висаріона, чудотв. Прп. Іларіона Нового, ігум. Далматської обителі, ісп.</t>
+  </si>
+  <si>
+    <t>07.06</t>
+  </si>
+  <si>
+    <t>Св. сщмч. Теодота (Богдана), єп. Анкирського</t>
+  </si>
+  <si>
+    <t>08.06</t>
+  </si>
+  <si>
+    <t>🕃 Перенесення мощів св. вмч. Теодора Тирона</t>
+  </si>
+  <si>
+    <t>09.06</t>
+  </si>
+  <si>
+    <t>Неділя 6-та після Пасхи, сліпородженого. 🕃 Св. Кирила, аєп. Олександрійського</t>
+  </si>
+  <si>
+    <t>10.06</t>
+  </si>
+  <si>
+    <t>Тиждень 6-ий після Пасхи. Св. сщмч. Тимотея, єп. Пруського</t>
+  </si>
+  <si>
+    <t>11.06</t>
+  </si>
+  <si>
+    <t>🕂 Свв. апп. Вартоломея й Варнави</t>
+  </si>
+  <si>
+    <t>Апп.:</t>
+  </si>
+  <si>
+    <t>#lk051b</t>
+  </si>
+  <si>
+    <t>12.06</t>
+  </si>
+  <si>
+    <t>Віддання Пасхи. 🕃 Прп. Онуфрія Великого Прп. Петра Афонського</t>
+  </si>
+  <si>
+    <t>13.06</t>
+  </si>
+  <si>
+    <t>🕀 Вознесення Господнє. Св. мц. Акилини Св. Трифилія, єп. Левкусії Кипрської Прп. Антонія Падуанського</t>
+  </si>
+  <si>
+    <t>14.06</t>
+  </si>
+  <si>
+    <t>Св. прор. Єлисея Св. Методія, патр. Царгородського</t>
+  </si>
+  <si>
+    <t>15.06</t>
+  </si>
+  <si>
+    <t>Св. прор. Амоса Прп. Єроніма, пресвіт. Стридонського</t>
+  </si>
+  <si>
+    <t>16.06</t>
+  </si>
+  <si>
+    <t>Неділя 7-ма після Пасхи, свв. отців I-го Вселенського Собору. Св. і чудотв. Тихона Аматунтського</t>
+  </si>
+  <si>
+    <t>17.06</t>
+  </si>
+  <si>
+    <t>Тиждень 7-ий після Пасхи. Свв. мчч. Мануїла, Савела й Ісмаїла Прп. Іпатія, ігум. Руфеніанського</t>
+  </si>
+  <si>
+    <t>18.06</t>
+  </si>
+  <si>
+    <t>Св. мч. Леонтія</t>
+  </si>
+  <si>
+    <t>19.06</t>
+  </si>
+  <si>
+    <t>🕂 Св. ап. Юди, брата Господнього</t>
+  </si>
+  <si>
+    <t>#ap077</t>
+  </si>
+  <si>
+    <t>20.06</t>
+  </si>
+  <si>
+    <t>Св. сщмч. Методія, єп. Патарського</t>
+  </si>
+  <si>
+    <t>21.06</t>
+  </si>
+  <si>
+    <t>Віддання Вознесіння. Св. мч. Юліана Тарсійського</t>
+  </si>
+  <si>
+    <t>22.06</t>
+  </si>
+  <si>
+    <t>Субота заупокійна. Св. сщмч. Євсевія, єп. Самосатського</t>
+  </si>
+  <si>
+    <t>23.06</t>
+  </si>
+  <si>
+    <t>🕀 Зіслання Святого Духа. П’ятдесятниця. Св. мц. Агрипіни</t>
+  </si>
+  <si>
+    <t>24.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Понеділок Святого Духа.  Тиждень 1-ий по Зісланні Святого Духа. Тиждень загальниці. 🕀 Різдво чесного і славн. прор., предтечі і хрестителя Господнього Івана </t>
+  </si>
+  <si>
+    <t>#ap112</t>
+  </si>
+  <si>
+    <t>#lk001</t>
+  </si>
+  <si>
+    <t>25.06</t>
+  </si>
+  <si>
+    <t>Св. прпмц. Февронії</t>
+  </si>
+  <si>
+    <t>26.06</t>
+  </si>
+  <si>
+    <t>Прп. Давида, що в Солуні Блаж. сщмч. Андрія Іщака, пресвіт. Блаж. сщмч. Миколи Конрада, пресвіт., і мч. Володимира Прийми, співця</t>
+  </si>
+  <si>
+    <t>27.06</t>
+  </si>
+  <si>
+    <t>🕁 Блаж. сщмч. Миколая Чарнецького і двадцяти чотирьох співмучеників; блаженного сщмч. Омеляна Ковча Прп. Сампсона, приятеля подорожніх й убогих</t>
+  </si>
+  <si>
+    <t>Свщнмчч.:</t>
+  </si>
+  <si>
+    <t>#ap233</t>
+  </si>
+  <si>
+    <t>#mt036</t>
+  </si>
+  <si>
+    <t>28.06</t>
+  </si>
+  <si>
+    <t>🕃 Перенесення мощів свв. безср. Кира і Івана</t>
+  </si>
+  <si>
+    <t>29.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Віддання П’ятдесятниці. 🕀 Свв. славних і всехвальних первоверховних апп. Петра й Павла </t>
+  </si>
+  <si>
+    <t>#ap193</t>
+  </si>
+  <si>
+    <t>#mt067a</t>
+  </si>
+  <si>
+    <t>30.06</t>
+  </si>
+  <si>
+    <t>Неділя 1-ша по Зісланні Святого Духа. Всіх святих. 🕂 Собор свв. славних і всехвальних дванадцяти апп. Блаж. сщмч. Василія Величковського</t>
+  </si>
+  <si>
+    <t>#mr012</t>
+  </si>
+  <si>
+    <t>#ap084</t>
+  </si>
+  <si>
+    <t>#mt020a</t>
+  </si>
+  <si>
+    <t>Неділя 2-га по Зісланні Святого Духа. Всіх святих українського народу. Св. Никифора, ісп.</t>
+  </si>
+  <si>
+    <t>Святим:</t>
+  </si>
+  <si>
+    <t>#ap099</t>
+  </si>
+  <si>
+    <t>#mt025</t>
+  </si>
+  <si>
+    <t>#mt010b</t>
+  </si>
+  <si>
+    <t>Тиждень 3-ий по Зісланні Святого Духа. Св. мч. Лукиліяна і тих, що з ним</t>
+  </si>
+  <si>
+    <t>#ap094</t>
+  </si>
+  <si>
+    <t>#mt034a</t>
+  </si>
+  <si>
+    <t>#ap095</t>
+  </si>
+  <si>
+    <t>#mt035</t>
+  </si>
+  <si>
+    <t>Св. сщмч. Доротея, єп. Тирського Св. мч. Косми, пресвіт. вірменського</t>
+  </si>
+  <si>
+    <t>#ap096a</t>
+  </si>
+  <si>
+    <t>#ap098</t>
+  </si>
+  <si>
+    <t>#mt037</t>
+  </si>
+  <si>
+    <t>🕀 Свято найсолодшого Господа Бога і Спаса нашого Ісуса Христа – Чоловіколюбця. Св. сщмч. Теодота (Богдана), єп. Анкирського</t>
+  </si>
+  <si>
+    <t>#ap306</t>
+  </si>
+  <si>
+    <t>#ap101</t>
+  </si>
+  <si>
+    <t>#iv009</t>
+  </si>
+  <si>
+    <t>#mt038b</t>
+  </si>
+  <si>
+    <t>Сострадання Пресвятої Богородиці. 🕃 Перенесення мощів св. вмч. Теодора Тирона</t>
+  </si>
+  <si>
+    <t>Сострадання:</t>
+  </si>
+  <si>
+    <t>#ap085</t>
+  </si>
+  <si>
+    <t>#mt024</t>
+  </si>
+  <si>
+    <t>Неділя 3-тя по Зісланні Святого Духа. 🕃 Св. Кирила, аєп. Олександрійського</t>
+  </si>
+  <si>
+    <t>#ap088a</t>
+  </si>
+  <si>
+    <t>#mt018</t>
+  </si>
+  <si>
+    <t>Тиждень 4-ий по Зісланні Святого Духа. Св. сщмч. Тимотея, єп. Пруського</t>
+  </si>
+  <si>
+    <t>#ap102</t>
+  </si>
+  <si>
+    <t>#ap104</t>
+  </si>
+  <si>
+    <t>🕃 Прп. Онуфрія Великого Прп. Петра Афонського</t>
+  </si>
+  <si>
+    <t>#ap105</t>
+  </si>
+  <si>
+    <t>#mt042</t>
+  </si>
+  <si>
+    <t>Св. мц. Акилини Св. Трифилія, єп. Левкусії Кипрської Прп. Антонія Падуанського</t>
+  </si>
+  <si>
+    <t>#ap106</t>
+  </si>
+  <si>
+    <t>#ap107</t>
+  </si>
+  <si>
+    <t>#mt044</t>
+  </si>
+  <si>
+    <t>#ap092</t>
+  </si>
+  <si>
+    <t>#mt026</t>
+  </si>
+  <si>
+    <t>Неділя 4-та по Зісланні Святого Духа. Св. і чудотв. Тихона Аматунтського</t>
+  </si>
+  <si>
+    <t>Тиждень 5-ий по Зісланні Святого Духа. Свв. мчч. Мануїла, Савела й Ісмаїла Прп. Іпатія, ігум. Руфеніанського</t>
+  </si>
+  <si>
+    <t>#ap109</t>
+  </si>
+  <si>
+    <t>#mt045</t>
+  </si>
+  <si>
+    <t>#ap114</t>
+  </si>
+  <si>
+    <t>#mt046a</t>
+  </si>
+  <si>
+    <t>#ap117</t>
+  </si>
+  <si>
+    <t>#mt048</t>
+  </si>
+  <si>
+    <t>#ap118</t>
+  </si>
+  <si>
+    <t>#mt049</t>
+  </si>
+  <si>
+    <t>Св. мч. Юліана Тарсійського</t>
+  </si>
+  <si>
+    <t>#ap120</t>
+  </si>
+  <si>
+    <t>#mt050</t>
+  </si>
+  <si>
+    <t>Св. сщмч. Євсевія, єп. Самосатського</t>
+  </si>
+  <si>
+    <t>#ap097</t>
+  </si>
+  <si>
+    <t>#mt030</t>
+  </si>
+  <si>
+    <t>Неділя 5-та по Зісланні Святого Духа. Св. мц. Агрипіни</t>
+  </si>
+  <si>
+    <t>#ap103</t>
+  </si>
+  <si>
+    <t>#mt028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тиждень 6-ий по Зісланні Святого Духа. 🕀 Різдво чесного і славн. прор., предтечі і хрестителя Господнього Івана </t>
+  </si>
+  <si>
+    <t>#ap122</t>
+  </si>
+  <si>
+    <t>#mt052a</t>
+  </si>
+  <si>
+    <t>#ap127</t>
+  </si>
+  <si>
+    <t>#mt053</t>
+  </si>
+  <si>
+    <t>Блаж. Мчч.:</t>
+  </si>
+  <si>
+    <t>#ap130a</t>
+  </si>
+  <si>
+    <t>#mt055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🕀 Свв. славних і всехвальних первоверховних апп. Петра й Павла </t>
+  </si>
+  <si>
+    <t>Неділя 6-та по Зісланні Святого Духа. 🕂 Собор свв. славних і всехвальних дванадцяти апп. Блаж. сщмч. Василія Величковського</t>
+  </si>
+  <si>
+    <t>#ap110</t>
+  </si>
+  <si>
+    <t>#mt029</t>
+  </si>
+  <si>
+    <t>#iv048b</t>
+  </si>
+  <si>
+    <t>#ap093</t>
+  </si>
+  <si>
+    <t>#mt041</t>
+  </si>
+  <si>
+    <t>#iv061с</t>
+  </si>
+  <si>
+    <t>#ap240</t>
   </si>
 </sst>
 </file>
@@ -953,7 +920,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1131,6 +1098,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1294,9 +1267,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% – колірна тема 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1356,11 +1330,11 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2024-5-u" connectionId="2" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2024-5-u" connectionId="2" xr16:uid="{4ADCA82F-5206-49BB-88B7-0E3FBEC2948B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2024-5-g" connectionId="1" xr16:uid="{00000000-0016-0000-0100-000001000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="2024-5-g" connectionId="1" xr16:uid="{6BF272E1-FBC0-4B28-BAC3-FE933D9CE053}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1659,21 +1633,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB93C344-77ED-4ADA-AF6A-85AFE27FE3FC}">
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="72.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -1684,44 +1657,56 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
+      </c>
+      <c r="H1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
+      </c>
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -1730,44 +1715,56 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
+      </c>
+      <c r="H3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>88</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s">
         <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>240</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -1775,126 +1772,102 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="J6" t="s">
         <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -1903,183 +1876,171 @@
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="J15" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -2088,171 +2049,183 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="J18" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>91</v>
+        <v>122</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>49</v>
+      </c>
+      <c r="I19" t="s">
+        <v>123</v>
       </c>
       <c r="J19" t="s">
-        <v>93</v>
+        <v>50</v>
+      </c>
+      <c r="K19" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="J20" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="H21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" t="s">
-        <v>213</v>
+        <v>53</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
-      </c>
-      <c r="K21" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>104</v>
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>55</v>
       </c>
       <c r="H22" t="s">
-        <v>105</v>
+        <v>56</v>
+      </c>
+      <c r="I22" t="s">
+        <v>57</v>
       </c>
       <c r="J22" t="s">
-        <v>106</v>
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="J23" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
@@ -2261,262 +2234,277 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>61</v>
+      </c>
+      <c r="I24" t="s">
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>114</v>
+        <v>62</v>
+      </c>
+      <c r="K24" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
-        <v>120</v>
-      </c>
-      <c r="K25" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="J26" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>127</v>
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>142</v>
       </c>
       <c r="H27" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="J28" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>69</v>
+      </c>
+      <c r="I29" t="s">
+        <v>149</v>
       </c>
       <c r="J29" t="s">
-        <v>137</v>
+        <v>70</v>
+      </c>
+      <c r="K29" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>71</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H31" t="s">
-        <v>144</v>
-      </c>
-      <c r="J31" t="s">
-        <v>145</v>
+        <v>72</v>
+      </c>
+      <c r="K30" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C509459-C842-4DA6-97EB-640F7667C282}">
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>150</v>
+        <v>226</v>
+      </c>
+      <c r="I2" t="s">
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>151</v>
+        <v>159</v>
+      </c>
+      <c r="K2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -2525,207 +2513,183 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J5" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="H8" t="s">
-        <v>174</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
+        <v>177</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" t="s">
-        <v>177</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="H9" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="J9" t="s">
-        <v>179</v>
-      </c>
-      <c r="K9" t="s">
-        <v>48</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -2734,183 +2698,171 @@
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="J10" t="s">
-        <v>182</v>
-      </c>
-      <c r="K10" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>184</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="J11" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H12" t="s">
         <v>186</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>187</v>
-      </c>
-      <c r="J12" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" t="s">
         <v>189</v>
       </c>
-      <c r="H13" t="s">
-        <v>190</v>
-      </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="H14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="J16" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -2919,183 +2871,174 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J17" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="H18" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="J18" t="s">
-        <v>205</v>
-      </c>
-      <c r="K18" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>206</v>
+        <v>122</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>207</v>
+        <v>200</v>
+      </c>
+      <c r="I19" t="s">
+        <v>123</v>
       </c>
       <c r="J19" t="s">
-        <v>208</v>
+        <v>201</v>
+      </c>
+      <c r="K19" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="H20" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="J20" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c r="H21" t="s">
-        <v>212</v>
-      </c>
-      <c r="I21" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J21" t="s">
-        <v>214</v>
-      </c>
-      <c r="K21" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="H22" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J22" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>210</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="J23" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
@@ -3104,195 +3047,176 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>112</v>
+        <v>213</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>220</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="H25" t="s">
-        <v>222</v>
-      </c>
-      <c r="I25" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="J25" t="s">
-        <v>223</v>
-      </c>
-      <c r="K25" t="s">
-        <v>121</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="J26" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>227</v>
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>218</v>
       </c>
       <c r="H27" t="s">
-        <v>228</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
-        <v>229</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H28" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="J28" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
+      </c>
+      <c r="F29" t="s">
+        <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>233</v>
+        <v>149</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="F30" t="s">
-        <v>236</v>
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>237</v>
+        <v>223</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H31" t="s">
-        <v>238</v>
-      </c>
-      <c r="J31" t="s">
-        <v>239</v>
+        <v>224</v>
+      </c>
+      <c r="K30" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>